--- a/frota.xlsx
+++ b/frota.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\TRANSPORTE\Compartilhadas\PREMIAÇÃO MOTORISTA\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex.alves\Downloads\BASE PREMIO PYTON\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1806,7 +1806,7 @@
         <v>105</v>
       </c>
       <c r="B93" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C93" t="s">
         <v>9</v>
